--- a/dados/triagem/rotulagem_registro.xlsx
+++ b/dados/triagem/rotulagem_registro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c4e299b2499aae62/Documentos/Acadêmico/Dissertação Mestrado/Dados/caixa-conversao-toolkit/dados/triagem/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="11_2BF596975533FE7E5F6E62F3585ED87656C2693A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEBAD7DE-B515-4B0B-8A7D-3ED7D1A250FC}"/>
+  <xr:revisionPtr revIDLastSave="493" documentId="11_2BF596975533FE7E5F6E62F3585ED87656C2693A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45C6D9B5-9301-46DE-ACB0-50A01AA51753}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4461" uniqueCount="1982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4844" uniqueCount="1982">
   <si>
     <t>item_id</t>
   </si>
@@ -8314,12 +8314,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -8334,10 +8340,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8355,6 +8364,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11295,6 +11308,9 @@
       <c r="J82" s="2" t="s">
         <v>338</v>
       </c>
+      <c r="K82" s="2" t="s">
+        <v>1977</v>
+      </c>
     </row>
     <row r="83" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
@@ -11324,6 +11340,9 @@
       <c r="J83" s="2" t="s">
         <v>342</v>
       </c>
+      <c r="K83" s="2" t="s">
+        <v>1978</v>
+      </c>
     </row>
     <row r="84" spans="1:11" ht="135" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
@@ -11356,6 +11375,9 @@
       <c r="J84" s="2" t="s">
         <v>347</v>
       </c>
+      <c r="K84" s="2" t="s">
+        <v>1978</v>
+      </c>
     </row>
     <row r="85" spans="1:11" ht="195" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
@@ -11383,6 +11405,9 @@
       <c r="J85" s="2" t="s">
         <v>351</v>
       </c>
+      <c r="K85" s="2" t="s">
+        <v>1978</v>
+      </c>
     </row>
     <row r="86" spans="1:11" ht="270" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
@@ -11412,6 +11437,9 @@
       <c r="J86" s="2" t="s">
         <v>354</v>
       </c>
+      <c r="K86" s="2" t="s">
+        <v>1978</v>
+      </c>
     </row>
     <row r="87" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
@@ -11442,6 +11470,9 @@
       <c r="J87" s="2" t="s">
         <v>358</v>
       </c>
+      <c r="K87" s="2" t="s">
+        <v>1978</v>
+      </c>
     </row>
     <row r="88" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
@@ -11471,6 +11502,9 @@
       <c r="J88" s="2" t="s">
         <v>362</v>
       </c>
+      <c r="K88" s="2" t="s">
+        <v>1978</v>
+      </c>
     </row>
     <row r="89" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
@@ -11500,6 +11534,9 @@
       <c r="J89" s="2" t="s">
         <v>365</v>
       </c>
+      <c r="K89" s="2" t="s">
+        <v>1978</v>
+      </c>
     </row>
     <row r="90" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
@@ -11527,6 +11564,9 @@
       <c r="J90" s="2" t="s">
         <v>369</v>
       </c>
+      <c r="K90" s="2" t="s">
+        <v>1978</v>
+      </c>
     </row>
     <row r="91" spans="1:11" ht="210" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
@@ -11554,6 +11594,9 @@
       <c r="J91" s="2" t="s">
         <v>373</v>
       </c>
+      <c r="K91" s="2" t="s">
+        <v>1978</v>
+      </c>
     </row>
     <row r="92" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
@@ -11581,6 +11624,9 @@
       <c r="J92" s="2" t="s">
         <v>376</v>
       </c>
+      <c r="K92" s="2" t="s">
+        <v>1977</v>
+      </c>
     </row>
     <row r="93" spans="1:11" ht="270" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
@@ -11610,6 +11656,9 @@
       <c r="J93" s="2" t="s">
         <v>379</v>
       </c>
+      <c r="K93" s="2" t="s">
+        <v>1978</v>
+      </c>
     </row>
     <row r="94" spans="1:11" ht="300" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
@@ -11642,6 +11691,9 @@
       <c r="J94" s="2" t="s">
         <v>383</v>
       </c>
+      <c r="K94" s="2" t="s">
+        <v>1978</v>
+      </c>
     </row>
     <row r="95" spans="1:11" ht="315" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
@@ -11671,6 +11723,9 @@
       <c r="J95" s="2" t="s">
         <v>387</v>
       </c>
+      <c r="K95" s="2" t="s">
+        <v>1978</v>
+      </c>
     </row>
     <row r="96" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
@@ -11700,8 +11755,11 @@
       <c r="J96" s="2" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="97" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K96" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>392</v>
       </c>
@@ -11729,8 +11787,11 @@
       <c r="J97" s="2" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="98" spans="1:10" ht="255" x14ac:dyDescent="0.25">
+      <c r="K97" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="255" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>395</v>
       </c>
@@ -11761,8 +11822,11 @@
       <c r="J98" s="2" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="99" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K98" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>400</v>
       </c>
@@ -11790,8 +11854,11 @@
       <c r="J99" s="2" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="100" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K99" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>404</v>
       </c>
@@ -11817,8 +11884,11 @@
       <c r="J100" s="2" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="101" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K100" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>407</v>
       </c>
@@ -11847,8 +11917,11 @@
       <c r="J101" s="2" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="102" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K101" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>412</v>
       </c>
@@ -11879,8 +11952,11 @@
       <c r="J102" s="2" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="103" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+      <c r="K102" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>418</v>
       </c>
@@ -11908,8 +11984,11 @@
       <c r="J103" s="2" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="104" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K103" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>422</v>
       </c>
@@ -11935,8 +12014,11 @@
       <c r="J104" s="2" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="105" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+      <c r="K104" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" ht="165" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>426</v>
       </c>
@@ -11962,8 +12044,11 @@
       <c r="J105" s="2" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="106" spans="1:10" ht="255" x14ac:dyDescent="0.25">
+      <c r="K105" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" ht="255" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>431</v>
       </c>
@@ -11991,8 +12076,11 @@
       <c r="J106" s="2" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="107" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K106" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>436</v>
       </c>
@@ -12020,8 +12108,11 @@
       <c r="J107" s="2" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="108" spans="1:10" ht="285" x14ac:dyDescent="0.25">
+      <c r="K107" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" ht="285" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>439</v>
       </c>
@@ -12050,8 +12141,11 @@
       <c r="J108" s="2" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="109" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K108" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>442</v>
       </c>
@@ -12082,8 +12176,11 @@
       <c r="J109" s="2" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="110" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K109" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>446</v>
       </c>
@@ -12111,8 +12208,11 @@
       <c r="J110" s="2" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="111" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K110" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>450</v>
       </c>
@@ -12141,8 +12241,11 @@
       <c r="J111" s="2" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="112" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K111" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>455</v>
       </c>
@@ -12171,8 +12274,11 @@
       <c r="J112" s="2" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="113" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K112" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>460</v>
       </c>
@@ -12201,8 +12307,11 @@
       <c r="J113" s="2" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="114" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K113" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>464</v>
       </c>
@@ -12230,8 +12339,11 @@
       <c r="J114" s="2" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="115" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K114" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>467</v>
       </c>
@@ -12259,8 +12371,11 @@
       <c r="J115" s="2" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K115" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>471</v>
       </c>
@@ -12289,8 +12404,11 @@
       <c r="J116" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="117" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K116" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>474</v>
       </c>
@@ -12316,8 +12434,11 @@
       <c r="J117" s="2" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="118" spans="1:10" ht="270" x14ac:dyDescent="0.25">
+      <c r="K117" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" ht="270" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>477</v>
       </c>
@@ -12348,8 +12469,11 @@
       <c r="J118" s="2" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="119" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K118" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>483</v>
       </c>
@@ -12380,8 +12504,11 @@
       <c r="J119" s="2" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="120" spans="1:10" ht="270" x14ac:dyDescent="0.25">
+      <c r="K119" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" ht="270" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>488</v>
       </c>
@@ -12407,8 +12534,11 @@
       <c r="J120" s="2" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="121" spans="1:10" ht="225" x14ac:dyDescent="0.25">
+      <c r="K120" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>493</v>
       </c>
@@ -12434,8 +12564,11 @@
       <c r="J121" s="2" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="122" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+      <c r="K121" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" ht="135" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>496</v>
       </c>
@@ -12461,8 +12594,11 @@
       <c r="J122" s="2" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="123" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K122" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>499</v>
       </c>
@@ -12488,8 +12624,11 @@
       <c r="J123" s="2" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="124" spans="1:10" ht="375" x14ac:dyDescent="0.25">
+      <c r="K123" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" ht="375" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>502</v>
       </c>
@@ -12517,8 +12656,11 @@
       <c r="J124" s="2" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="125" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K124" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>506</v>
       </c>
@@ -12544,8 +12686,11 @@
       <c r="J125" s="2" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="126" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K125" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>509</v>
       </c>
@@ -12571,8 +12716,11 @@
       <c r="J126" s="2" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="127" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K126" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>513</v>
       </c>
@@ -12601,8 +12749,11 @@
       <c r="J127" s="2" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="128" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K127" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>519</v>
       </c>
@@ -12631,8 +12782,11 @@
       <c r="J128" s="2" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="129" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K128" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>521</v>
       </c>
@@ -12663,8 +12817,9 @@
       <c r="J129" s="2" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="130" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K129" s="2"/>
+    </row>
+    <row r="130" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>526</v>
       </c>
@@ -12692,8 +12847,11 @@
       <c r="J130" s="2" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="131" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K130" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>530</v>
       </c>
@@ -12719,8 +12877,11 @@
       <c r="J131" s="2" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="132" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K131" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>533</v>
       </c>
@@ -12746,8 +12907,11 @@
       <c r="J132" s="2" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="133" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K132" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>536</v>
       </c>
@@ -12776,8 +12940,11 @@
       <c r="J133" s="2" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="134" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K133" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>541</v>
       </c>
@@ -12805,8 +12972,11 @@
       <c r="J134" s="2" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="135" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="K134" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>545</v>
       </c>
@@ -12834,8 +13004,11 @@
       <c r="J135" s="2" t="s">
         <v>548</v>
       </c>
-    </row>
-    <row r="136" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+      <c r="K135" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" ht="165" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>549</v>
       </c>
@@ -12864,8 +13037,11 @@
       <c r="J136" s="2" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="137" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K136" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>554</v>
       </c>
@@ -12893,8 +13069,11 @@
       <c r="J137" s="2" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="138" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K137" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>559</v>
       </c>
@@ -12925,8 +13104,11 @@
       <c r="J138" s="2" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="139" spans="1:10" ht="255" x14ac:dyDescent="0.25">
+      <c r="K138" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" ht="255" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>563</v>
       </c>
@@ -12957,8 +13139,11 @@
       <c r="J139" s="2" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="140" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K139" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>567</v>
       </c>
@@ -12986,8 +13171,11 @@
       <c r="J140" s="2" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="141" spans="1:10" ht="255" x14ac:dyDescent="0.25">
+      <c r="K140" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" ht="255" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>570</v>
       </c>
@@ -13016,8 +13204,11 @@
       <c r="J141" s="2" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="142" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K141" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>574</v>
       </c>
@@ -13048,8 +13239,11 @@
       <c r="J142" s="2" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="143" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K142" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>579</v>
       </c>
@@ -13080,8 +13274,11 @@
       <c r="J143" s="2" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="144" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K143" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>583</v>
       </c>
@@ -13112,8 +13309,11 @@
       <c r="J144" s="2" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="145" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="K144" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>588</v>
       </c>
@@ -13144,8 +13344,11 @@
       <c r="J145" s="2" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="146" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K145" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>593</v>
       </c>
@@ -13173,8 +13376,11 @@
       <c r="J146" s="2" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="147" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K146" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>596</v>
       </c>
@@ -13202,8 +13408,11 @@
       <c r="J147" s="2" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="148" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K147" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>600</v>
       </c>
@@ -13231,8 +13440,11 @@
       <c r="J148" s="2" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="149" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K148" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>604</v>
       </c>
@@ -13260,8 +13472,11 @@
       <c r="J149" s="2" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="150" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K149" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>608</v>
       </c>
@@ -13289,8 +13504,11 @@
       <c r="J150" s="2" t="s">
         <v>610</v>
       </c>
-    </row>
-    <row r="151" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K150" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>611</v>
       </c>
@@ -13318,8 +13536,11 @@
       <c r="J151" s="2" t="s">
         <v>616</v>
       </c>
-    </row>
-    <row r="152" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K151" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>617</v>
       </c>
@@ -13350,8 +13571,11 @@
       <c r="J152" s="2" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="153" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K152" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>621</v>
       </c>
@@ -13382,8 +13606,11 @@
       <c r="J153" s="2" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="154" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K153" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>625</v>
       </c>
@@ -13411,8 +13638,11 @@
       <c r="J154" s="2" t="s">
         <v>628</v>
       </c>
-    </row>
-    <row r="155" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K154" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>629</v>
       </c>
@@ -13440,8 +13670,11 @@
       <c r="J155" s="2" t="s">
         <v>631</v>
       </c>
-    </row>
-    <row r="156" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K155" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>632</v>
       </c>
@@ -13469,8 +13702,11 @@
       <c r="J156" s="2" t="s">
         <v>634</v>
       </c>
-    </row>
-    <row r="157" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K156" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>635</v>
       </c>
@@ -13498,8 +13734,11 @@
       <c r="J157" s="2" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="158" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K157" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>637</v>
       </c>
@@ -13528,8 +13767,11 @@
       <c r="J158" s="2" t="s">
         <v>640</v>
       </c>
-    </row>
-    <row r="159" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K158" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>641</v>
       </c>
@@ -13557,8 +13799,11 @@
       <c r="J159" s="2" t="s">
         <v>644</v>
       </c>
-    </row>
-    <row r="160" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K159" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>645</v>
       </c>
@@ -13586,8 +13831,11 @@
       <c r="J160" s="2" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="161" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+      <c r="K160" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" ht="135" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>648</v>
       </c>
@@ -13618,8 +13866,11 @@
       <c r="J161" s="2" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="162" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K161" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>653</v>
       </c>
@@ -13650,8 +13901,11 @@
       <c r="J162" s="2" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="163" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K162" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>657</v>
       </c>
@@ -13682,8 +13936,11 @@
       <c r="J163" s="2" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="164" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+      <c r="K163" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>661</v>
       </c>
@@ -13712,8 +13969,11 @@
       <c r="J164" s="2" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="165" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K164" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>665</v>
       </c>
@@ -13744,8 +14004,11 @@
       <c r="J165" s="2" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="166" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="K165" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>670</v>
       </c>
@@ -13776,8 +14039,11 @@
       <c r="J166" s="2" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="167" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K166" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>673</v>
       </c>
@@ -13808,8 +14074,11 @@
       <c r="J167" s="2" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="168" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+      <c r="K167" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>678</v>
       </c>
@@ -13840,8 +14109,11 @@
       <c r="J168" s="2" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="169" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K168" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>682</v>
       </c>
@@ -13872,8 +14144,11 @@
       <c r="J169" s="2" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="170" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K169" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>687</v>
       </c>
@@ -13904,8 +14179,11 @@
       <c r="J170" s="2" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="171" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K170" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>691</v>
       </c>
@@ -13937,7 +14215,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="172" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>695</v>
       </c>
@@ -13969,7 +14247,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="173" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>699</v>
       </c>
@@ -14000,8 +14278,11 @@
       <c r="J173" s="2" t="s">
         <v>702</v>
       </c>
-    </row>
-    <row r="174" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="K173" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>703</v>
       </c>
@@ -14029,8 +14310,11 @@
       <c r="J174" s="2" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="175" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K174" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>707</v>
       </c>
@@ -14061,8 +14345,11 @@
       <c r="J175" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="176" spans="1:10" ht="270" x14ac:dyDescent="0.25">
+      <c r="K175" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" ht="270" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>710</v>
       </c>
@@ -14093,8 +14380,11 @@
       <c r="J176" s="2" t="s">
         <v>714</v>
       </c>
-    </row>
-    <row r="177" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+      <c r="K176" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" ht="135" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>715</v>
       </c>
@@ -14122,8 +14412,11 @@
       <c r="J177" s="2" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="178" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K177" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>719</v>
       </c>
@@ -14154,8 +14447,11 @@
       <c r="J178" s="2" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="179" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K178" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>723</v>
       </c>
@@ -14181,8 +14477,11 @@
       <c r="J179" s="2" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="180" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K179" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>727</v>
       </c>
@@ -14211,8 +14510,11 @@
       <c r="J180" s="2" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="181" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K180" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>730</v>
       </c>
@@ -14241,8 +14543,11 @@
       <c r="J181" s="2" t="s">
         <v>732</v>
       </c>
-    </row>
-    <row r="182" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K181" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>733</v>
       </c>
@@ -14271,8 +14576,11 @@
       <c r="J182" s="2" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="183" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K182" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>737</v>
       </c>
@@ -14301,8 +14609,11 @@
       <c r="J183" s="2" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="184" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K183" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>739</v>
       </c>
@@ -14331,8 +14642,11 @@
       <c r="J184" s="2" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="185" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K184" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>741</v>
       </c>
@@ -14360,8 +14674,11 @@
       <c r="J185" s="2" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="186" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K185" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>743</v>
       </c>
@@ -14390,8 +14707,11 @@
       <c r="J186" s="2" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="187" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K186" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>746</v>
       </c>
@@ -14420,8 +14740,11 @@
       <c r="J187" s="2" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="188" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K187" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>748</v>
       </c>
@@ -14449,8 +14772,11 @@
       <c r="J188" s="2" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="189" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K188" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>751</v>
       </c>
@@ -14481,8 +14807,11 @@
       <c r="J189" s="2" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="190" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K189" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>754</v>
       </c>
@@ -14510,8 +14839,11 @@
       <c r="J190" s="2" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="191" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K190" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>756</v>
       </c>
@@ -14540,8 +14872,11 @@
       <c r="J191" s="2" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="192" spans="1:10" ht="375" x14ac:dyDescent="0.25">
+      <c r="K191" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" ht="375" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>760</v>
       </c>
@@ -14564,11 +14899,14 @@
       <c r="I192" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="J192" s="2" t="s">
+      <c r="J192" s="3" t="s">
         <v>763</v>
       </c>
-    </row>
-    <row r="193" spans="1:10" ht="405" x14ac:dyDescent="0.25">
+      <c r="K192" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" ht="405" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>764</v>
       </c>
@@ -14593,11 +14931,14 @@
       <c r="I193" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="J193" s="2" t="s">
+      <c r="J193" s="3" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="194" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+      <c r="K193" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" ht="210" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>768</v>
       </c>
@@ -14623,8 +14964,11 @@
       <c r="J194" s="2" t="s">
         <v>770</v>
       </c>
-    </row>
-    <row r="195" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K194" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>771</v>
       </c>
@@ -14652,8 +14996,9 @@
       <c r="J195" s="2" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="196" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K195" s="2"/>
+    </row>
+    <row r="196" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>776</v>
       </c>
@@ -14681,8 +15026,11 @@
       <c r="J196" s="2" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="197" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K196" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>780</v>
       </c>
@@ -14710,8 +15058,11 @@
       <c r="J197" s="2" t="s">
         <v>782</v>
       </c>
-    </row>
-    <row r="198" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K197" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>783</v>
       </c>
@@ -14737,8 +15088,11 @@
       <c r="J198" s="2" t="s">
         <v>784</v>
       </c>
-    </row>
-    <row r="199" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K198" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>785</v>
       </c>
@@ -14767,7 +15121,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="200" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>789</v>
       </c>
@@ -14795,8 +15149,11 @@
       <c r="J200" s="2" t="s">
         <v>791</v>
       </c>
-    </row>
-    <row r="201" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K200" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>792</v>
       </c>
@@ -14827,8 +15184,11 @@
       <c r="J201" s="2" t="s">
         <v>796</v>
       </c>
-    </row>
-    <row r="202" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K201" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>797</v>
       </c>
@@ -14859,8 +15219,11 @@
       <c r="J202" s="2" t="s">
         <v>800</v>
       </c>
-    </row>
-    <row r="203" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K202" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>801</v>
       </c>
@@ -14891,8 +15254,11 @@
       <c r="J203" s="2" t="s">
         <v>804</v>
       </c>
-    </row>
-    <row r="204" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K203" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>805</v>
       </c>
@@ -14923,8 +15289,11 @@
       <c r="J204" s="2" t="s">
         <v>807</v>
       </c>
-    </row>
-    <row r="205" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K204" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>808</v>
       </c>
@@ -14955,8 +15324,11 @@
       <c r="J205" s="2" t="s">
         <v>811</v>
       </c>
-    </row>
-    <row r="206" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K205" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>812</v>
       </c>
@@ -14984,8 +15356,11 @@
       <c r="J206" s="2" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="207" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K206" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>816</v>
       </c>
@@ -15016,8 +15391,11 @@
       <c r="J207" s="2" t="s">
         <v>821</v>
       </c>
-    </row>
-    <row r="208" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="K207" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>822</v>
       </c>
@@ -15046,8 +15424,11 @@
       <c r="J208" s="2" t="s">
         <v>825</v>
       </c>
-    </row>
-    <row r="209" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K208" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>826</v>
       </c>
@@ -15078,8 +15459,11 @@
       <c r="J209" s="2" t="s">
         <v>829</v>
       </c>
-    </row>
-    <row r="210" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K209" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>830</v>
       </c>
@@ -15110,8 +15494,11 @@
       <c r="J210" s="2" t="s">
         <v>833</v>
       </c>
-    </row>
-    <row r="211" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K210" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>834</v>
       </c>
@@ -15139,8 +15526,11 @@
       <c r="J211" s="2" t="s">
         <v>837</v>
       </c>
-    </row>
-    <row r="212" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K211" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>838</v>
       </c>
@@ -15168,8 +15558,11 @@
       <c r="J212" s="2" t="s">
         <v>840</v>
       </c>
-    </row>
-    <row r="213" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K212" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>841</v>
       </c>
@@ -15197,8 +15590,11 @@
       <c r="J213" s="2" t="s">
         <v>844</v>
       </c>
-    </row>
-    <row r="214" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K213" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>845</v>
       </c>
@@ -15226,8 +15622,11 @@
       <c r="J214" s="2" t="s">
         <v>848</v>
       </c>
-    </row>
-    <row r="215" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K214" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>849</v>
       </c>
@@ -15255,8 +15654,11 @@
       <c r="J215" s="2" t="s">
         <v>852</v>
       </c>
-    </row>
-    <row r="216" spans="1:10" ht="225" x14ac:dyDescent="0.25">
+      <c r="K215" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>853</v>
       </c>
@@ -15285,7 +15687,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="217" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>858</v>
       </c>
@@ -15314,8 +15716,11 @@
       <c r="J217" s="2" t="s">
         <v>861</v>
       </c>
-    </row>
-    <row r="218" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K217" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>862</v>
       </c>
@@ -15346,8 +15751,11 @@
       <c r="J218" s="2" t="s">
         <v>864</v>
       </c>
-    </row>
-    <row r="219" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+      <c r="K218" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>865</v>
       </c>
@@ -15375,8 +15783,11 @@
       <c r="J219" s="2" t="s">
         <v>868</v>
       </c>
-    </row>
-    <row r="220" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K219" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>869</v>
       </c>
@@ -15404,8 +15815,11 @@
       <c r="J220" s="2" t="s">
         <v>873</v>
       </c>
-    </row>
-    <row r="221" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+      <c r="K220" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>874</v>
       </c>
@@ -15436,8 +15850,11 @@
       <c r="J221" s="2" t="s">
         <v>877</v>
       </c>
-    </row>
-    <row r="222" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="K221" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>878</v>
       </c>
@@ -15463,8 +15880,11 @@
       <c r="J222" s="2" t="s">
         <v>881</v>
       </c>
-    </row>
-    <row r="223" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="K222" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>882</v>
       </c>
@@ -15492,8 +15912,11 @@
       <c r="J223" s="2" t="s">
         <v>884</v>
       </c>
-    </row>
-    <row r="224" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+      <c r="K223" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11" ht="180" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>885</v>
       </c>
@@ -15521,8 +15944,11 @@
       <c r="J224" s="2" t="s">
         <v>887</v>
       </c>
-    </row>
-    <row r="225" spans="1:10" ht="225" x14ac:dyDescent="0.25">
+      <c r="K224" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>888</v>
       </c>
@@ -15550,8 +15976,11 @@
       <c r="J225" s="2" t="s">
         <v>890</v>
       </c>
-    </row>
-    <row r="226" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K225" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>891</v>
       </c>
@@ -15582,8 +16011,11 @@
       <c r="J226" s="2" t="s">
         <v>893</v>
       </c>
-    </row>
-    <row r="227" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+      <c r="K226" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" ht="165" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>894</v>
       </c>
@@ -15611,8 +16043,11 @@
       <c r="J227" s="2" t="s">
         <v>899</v>
       </c>
-    </row>
-    <row r="228" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K227" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>900</v>
       </c>
@@ -15643,8 +16078,11 @@
       <c r="J228" s="2" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="229" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K228" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>905</v>
       </c>
@@ -15675,8 +16113,11 @@
       <c r="J229" s="2" t="s">
         <v>910</v>
       </c>
-    </row>
-    <row r="230" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K229" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>911</v>
       </c>
@@ -15704,8 +16145,11 @@
       <c r="J230" s="2" t="s">
         <v>913</v>
       </c>
-    </row>
-    <row r="231" spans="1:10" ht="390" x14ac:dyDescent="0.25">
+      <c r="K230" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" ht="390" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>914</v>
       </c>
@@ -15734,8 +16178,11 @@
       <c r="J231" s="2" t="s">
         <v>917</v>
       </c>
-    </row>
-    <row r="232" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K231" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>918</v>
       </c>
@@ -15764,8 +16211,11 @@
       <c r="J232" s="2" t="s">
         <v>921</v>
       </c>
-    </row>
-    <row r="233" spans="1:10" ht="330" x14ac:dyDescent="0.25">
+      <c r="K232" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11" ht="330" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>922</v>
       </c>
@@ -15794,8 +16244,11 @@
       <c r="J233" s="2" t="s">
         <v>924</v>
       </c>
-    </row>
-    <row r="234" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K233" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>925</v>
       </c>
@@ -15824,8 +16277,11 @@
       <c r="J234" s="2" t="s">
         <v>928</v>
       </c>
-    </row>
-    <row r="235" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K234" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>929</v>
       </c>
@@ -15853,8 +16309,11 @@
       <c r="J235" s="2" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="236" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+      <c r="K235" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11" ht="210" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>933</v>
       </c>
@@ -15882,8 +16341,11 @@
       <c r="J236" s="2" t="s">
         <v>936</v>
       </c>
-    </row>
-    <row r="237" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+      <c r="K236" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11" ht="210" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>937</v>
       </c>
@@ -15912,8 +16374,11 @@
       <c r="J237" s="2" t="s">
         <v>940</v>
       </c>
-    </row>
-    <row r="238" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K237" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>941</v>
       </c>
@@ -15941,8 +16406,11 @@
       <c r="J238" s="2" t="s">
         <v>943</v>
       </c>
-    </row>
-    <row r="239" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K238" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>944</v>
       </c>
@@ -15973,8 +16441,11 @@
       <c r="J239" s="2" t="s">
         <v>949</v>
       </c>
-    </row>
-    <row r="240" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K239" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>950</v>
       </c>
@@ -16002,8 +16473,11 @@
       <c r="J240" s="2" t="s">
         <v>954</v>
       </c>
-    </row>
-    <row r="241" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K240" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>955</v>
       </c>
@@ -16029,8 +16503,11 @@
       <c r="J241" s="2" t="s">
         <v>957</v>
       </c>
-    </row>
-    <row r="242" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K241" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>958</v>
       </c>
@@ -16061,8 +16538,11 @@
       <c r="J242" s="2" t="s">
         <v>961</v>
       </c>
-    </row>
-    <row r="243" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K242" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>962</v>
       </c>
@@ -16088,8 +16568,11 @@
       <c r="J243" s="2" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="244" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="K243" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>966</v>
       </c>
@@ -16117,8 +16600,11 @@
       <c r="J244" s="2" t="s">
         <v>968</v>
       </c>
-    </row>
-    <row r="245" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+      <c r="K244" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="245" spans="1:11" ht="180" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>969</v>
       </c>
@@ -16149,8 +16635,11 @@
       <c r="J245" s="2" t="s">
         <v>974</v>
       </c>
-    </row>
-    <row r="246" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K245" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>975</v>
       </c>
@@ -16178,8 +16667,11 @@
       <c r="J246" s="2" t="s">
         <v>978</v>
       </c>
-    </row>
-    <row r="247" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+      <c r="K246" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="247" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>979</v>
       </c>
@@ -16208,8 +16700,11 @@
       <c r="J247" s="2" t="s">
         <v>984</v>
       </c>
-    </row>
-    <row r="248" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="K247" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="248" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>985</v>
       </c>
@@ -16238,8 +16733,11 @@
       <c r="J248" s="2" t="s">
         <v>987</v>
       </c>
-    </row>
-    <row r="249" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+      <c r="K248" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="249" spans="1:11" ht="180" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>988</v>
       </c>
@@ -16268,8 +16766,11 @@
       <c r="J249" s="2" t="s">
         <v>992</v>
       </c>
-    </row>
-    <row r="250" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K249" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="250" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>993</v>
       </c>
@@ -16296,7 +16797,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="251" spans="1:10" ht="390" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:11" ht="390" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>996</v>
       </c>
@@ -16327,8 +16828,11 @@
       <c r="J251" s="2" t="s">
         <v>1000</v>
       </c>
-    </row>
-    <row r="252" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K251" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="252" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1001</v>
       </c>
@@ -16357,8 +16861,11 @@
       <c r="J252" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="253" spans="1:10" ht="240" x14ac:dyDescent="0.25">
+      <c r="K252" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="253" spans="1:11" ht="240" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>1005</v>
       </c>
@@ -16389,8 +16896,11 @@
       <c r="J253" s="2" t="s">
         <v>1008</v>
       </c>
-    </row>
-    <row r="254" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+      <c r="K253" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="254" spans="1:11" ht="165" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>1009</v>
       </c>
@@ -16418,8 +16928,11 @@
       <c r="J254" s="2" t="s">
         <v>1011</v>
       </c>
-    </row>
-    <row r="255" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+      <c r="K254" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="255" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>1012</v>
       </c>
@@ -16448,8 +16961,11 @@
       <c r="J255" s="2" t="s">
         <v>1015</v>
       </c>
-    </row>
-    <row r="256" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K255" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="256" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>1016</v>
       </c>
@@ -16477,8 +16993,11 @@
       <c r="J256" s="2" t="s">
         <v>1019</v>
       </c>
-    </row>
-    <row r="257" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K256" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="257" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>1020</v>
       </c>
@@ -16507,8 +17026,11 @@
       <c r="J257" s="2" t="s">
         <v>1023</v>
       </c>
-    </row>
-    <row r="258" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="K257" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="258" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>1024</v>
       </c>
@@ -16534,8 +17056,11 @@
       <c r="J258" s="2" t="s">
         <v>1027</v>
       </c>
-    </row>
-    <row r="259" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K258" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="259" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>1028</v>
       </c>
@@ -16563,8 +17088,11 @@
       <c r="J259" s="2" t="s">
         <v>1030</v>
       </c>
-    </row>
-    <row r="260" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K259" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="260" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>1031</v>
       </c>
@@ -16590,8 +17118,11 @@
       <c r="J260" s="2" t="s">
         <v>1034</v>
       </c>
-    </row>
-    <row r="261" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K260" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="261" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>1035</v>
       </c>
@@ -16617,8 +17148,11 @@
       <c r="J261" s="2" t="s">
         <v>1038</v>
       </c>
-    </row>
-    <row r="262" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K261" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="262" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>1039</v>
       </c>
@@ -16644,8 +17178,11 @@
       <c r="J262" s="2" t="s">
         <v>1042</v>
       </c>
-    </row>
-    <row r="263" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K262" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="263" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>1043</v>
       </c>
@@ -16671,8 +17208,11 @@
       <c r="J263" s="2" t="s">
         <v>1046</v>
       </c>
-    </row>
-    <row r="264" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K263" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="264" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>1047</v>
       </c>
@@ -16703,8 +17243,11 @@
       <c r="J264" s="2" t="s">
         <v>1051</v>
       </c>
-    </row>
-    <row r="265" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K264" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="265" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>1052</v>
       </c>
@@ -16733,8 +17276,11 @@
       <c r="J265" s="2" t="s">
         <v>1055</v>
       </c>
-    </row>
-    <row r="266" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K265" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="266" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>1056</v>
       </c>
@@ -16760,8 +17306,11 @@
       <c r="J266" s="2" t="s">
         <v>1059</v>
       </c>
-    </row>
-    <row r="267" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K266" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="267" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>1060</v>
       </c>
@@ -16787,8 +17336,11 @@
       <c r="J267" s="2" t="s">
         <v>1062</v>
       </c>
-    </row>
-    <row r="268" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K267" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="268" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>1063</v>
       </c>
@@ -16814,8 +17366,11 @@
       <c r="J268" s="2" t="s">
         <v>1066</v>
       </c>
-    </row>
-    <row r="269" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K268" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="269" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>1067</v>
       </c>
@@ -16844,8 +17399,11 @@
       <c r="J269" s="2" t="s">
         <v>1071</v>
       </c>
-    </row>
-    <row r="270" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K269" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="270" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>1072</v>
       </c>
@@ -16873,8 +17431,11 @@
       <c r="J270" s="2" t="s">
         <v>1076</v>
       </c>
-    </row>
-    <row r="271" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K270" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="271" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>1077</v>
       </c>
@@ -16902,8 +17463,11 @@
       <c r="J271" s="2" t="s">
         <v>1080</v>
       </c>
-    </row>
-    <row r="272" spans="1:10" ht="225" x14ac:dyDescent="0.25">
+      <c r="K271" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="272" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>1081</v>
       </c>
@@ -16932,8 +17496,11 @@
       <c r="J272" s="2" t="s">
         <v>1085</v>
       </c>
-    </row>
-    <row r="273" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+      <c r="K272" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="273" spans="1:11" ht="180" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>1086</v>
       </c>
@@ -16962,8 +17529,11 @@
       <c r="J273" s="2" t="s">
         <v>1088</v>
       </c>
-    </row>
-    <row r="274" spans="1:10" ht="240" x14ac:dyDescent="0.25">
+      <c r="K273" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="274" spans="1:11" ht="240" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>1089</v>
       </c>
@@ -16991,11 +17561,14 @@
       <c r="I274" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="J274" s="2" t="s">
+      <c r="J274" s="3" t="s">
         <v>1094</v>
       </c>
-    </row>
-    <row r="275" spans="1:10" ht="255" x14ac:dyDescent="0.25">
+      <c r="K274" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="275" spans="1:11" ht="255" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>1095</v>
       </c>
@@ -17021,8 +17594,11 @@
       <c r="J275" s="2" t="s">
         <v>1097</v>
       </c>
-    </row>
-    <row r="276" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K275" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="276" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>1098</v>
       </c>
@@ -17051,8 +17627,11 @@
       <c r="J276" s="2" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="277" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K276" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="277" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1100</v>
       </c>
@@ -17081,7 +17660,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="278" spans="1:10" ht="390" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:11" ht="390" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1104</v>
       </c>
@@ -17110,7 +17689,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="279" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:11" ht="135" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1108</v>
       </c>
@@ -17139,7 +17718,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="280" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>1112</v>
       </c>
@@ -17168,7 +17747,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="281" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:11" ht="135" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>1116</v>
       </c>
@@ -17197,7 +17776,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="282" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>1120</v>
       </c>
@@ -17228,8 +17807,11 @@
       <c r="J282" s="2" t="s">
         <v>1123</v>
       </c>
-    </row>
-    <row r="283" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K282" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="283" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1124</v>
       </c>
@@ -17256,7 +17838,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="284" spans="1:10" ht="330" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:11" ht="330" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1127</v>
       </c>
@@ -17283,7 +17865,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="285" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:11" ht="165" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>1131</v>
       </c>
@@ -17309,8 +17891,11 @@
       <c r="J285" s="2" t="s">
         <v>1133</v>
       </c>
-    </row>
-    <row r="286" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K285" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="286" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>1134</v>
       </c>
@@ -17339,8 +17924,11 @@
       <c r="J286" s="2" t="s">
         <v>1138</v>
       </c>
-    </row>
-    <row r="287" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K286" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="287" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>1139</v>
       </c>
@@ -17371,8 +17959,11 @@
       <c r="J287" s="2" t="s">
         <v>1142</v>
       </c>
-    </row>
-    <row r="288" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K287" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="288" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>1143</v>
       </c>
@@ -17398,8 +17989,11 @@
       <c r="J288" s="2" t="s">
         <v>1145</v>
       </c>
-    </row>
-    <row r="289" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K288" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="289" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>1146</v>
       </c>
@@ -17428,8 +18022,11 @@
       <c r="J289" s="2" t="s">
         <v>1148</v>
       </c>
-    </row>
-    <row r="290" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K289" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="290" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>1149</v>
       </c>
@@ -17458,8 +18055,11 @@
       <c r="J290" s="2" t="s">
         <v>1153</v>
       </c>
-    </row>
-    <row r="291" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K290" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="291" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>1154</v>
       </c>
@@ -17488,8 +18088,9 @@
       <c r="J291" s="2" t="s">
         <v>1156</v>
       </c>
-    </row>
-    <row r="292" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K291" s="2"/>
+    </row>
+    <row r="292" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>1157</v>
       </c>
@@ -17518,8 +18119,11 @@
       <c r="J292" s="2" t="s">
         <v>1160</v>
       </c>
-    </row>
-    <row r="293" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="K292" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="293" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>1161</v>
       </c>
@@ -17550,8 +18154,11 @@
       <c r="J293" s="2" t="s">
         <v>1164</v>
       </c>
-    </row>
-    <row r="294" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+      <c r="K293" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="294" spans="1:11" ht="165" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>1165</v>
       </c>
@@ -17580,8 +18187,11 @@
       <c r="J294" s="2" t="s">
         <v>1168</v>
       </c>
-    </row>
-    <row r="295" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+      <c r="K294" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="295" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1169</v>
       </c>
@@ -17607,8 +18217,11 @@
       <c r="J295" s="2" t="s">
         <v>1171</v>
       </c>
-    </row>
-    <row r="296" spans="1:10" ht="225" x14ac:dyDescent="0.25">
+      <c r="K295" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="296" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>1172</v>
       </c>
@@ -17639,8 +18252,11 @@
       <c r="J296" s="2" t="s">
         <v>1175</v>
       </c>
-    </row>
-    <row r="297" spans="1:10" ht="225" x14ac:dyDescent="0.25">
+      <c r="K296" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="297" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>1176</v>
       </c>
@@ -17669,8 +18285,11 @@
       <c r="J297" s="2" t="s">
         <v>1179</v>
       </c>
-    </row>
-    <row r="298" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K297" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="298" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>1180</v>
       </c>
@@ -17699,8 +18318,11 @@
       <c r="J298" s="2" t="s">
         <v>1183</v>
       </c>
-    </row>
-    <row r="299" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K298" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="299" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>1184</v>
       </c>
@@ -17729,8 +18351,11 @@
       <c r="J299" s="2" t="s">
         <v>1188</v>
       </c>
-    </row>
-    <row r="300" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K299" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="300" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>1189</v>
       </c>
@@ -17759,8 +18384,11 @@
       <c r="J300" s="2" t="s">
         <v>1193</v>
       </c>
-    </row>
-    <row r="301" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K300" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="301" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>1194</v>
       </c>
@@ -17789,8 +18417,11 @@
       <c r="J301" s="2" t="s">
         <v>1196</v>
       </c>
-    </row>
-    <row r="302" spans="1:10" ht="195" x14ac:dyDescent="0.25">
+      <c r="K301" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="302" spans="1:11" ht="195" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>1197</v>
       </c>
@@ -17816,8 +18447,11 @@
       <c r="J302" s="2" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="303" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K302" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="303" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>1201</v>
       </c>
@@ -17846,8 +18480,11 @@
       <c r="J303" s="2" t="s">
         <v>1205</v>
       </c>
-    </row>
-    <row r="304" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+      <c r="K303" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="304" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>1206</v>
       </c>
@@ -17876,8 +18513,11 @@
       <c r="J304" s="2" t="s">
         <v>1210</v>
       </c>
-    </row>
-    <row r="305" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+      <c r="K304" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="305" spans="1:11" ht="135" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>1211</v>
       </c>
@@ -17906,8 +18546,11 @@
       <c r="J305" s="2" t="s">
         <v>1215</v>
       </c>
-    </row>
-    <row r="306" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K305" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="306" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>1216</v>
       </c>
@@ -17933,8 +18576,11 @@
       <c r="J306" s="2" t="s">
         <v>1218</v>
       </c>
-    </row>
-    <row r="307" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="K306" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="307" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>1219</v>
       </c>
@@ -17962,8 +18608,11 @@
       <c r="J307" s="2" t="s">
         <v>1221</v>
       </c>
-    </row>
-    <row r="308" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+      <c r="K307" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="308" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>1222</v>
       </c>
@@ -17992,8 +18641,11 @@
       <c r="J308" s="2" t="s">
         <v>1226</v>
       </c>
-    </row>
-    <row r="309" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K308" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="309" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>1227</v>
       </c>
@@ -18022,8 +18674,11 @@
       <c r="J309" s="2" t="s">
         <v>1230</v>
       </c>
-    </row>
-    <row r="310" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K309" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="310" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>1231</v>
       </c>
@@ -18052,7 +18707,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="311" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>1235</v>
       </c>
@@ -18080,8 +18735,11 @@
       <c r="J311" s="2" t="s">
         <v>1237</v>
       </c>
-    </row>
-    <row r="312" spans="1:10" ht="240" x14ac:dyDescent="0.25">
+      <c r="K311" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="312" spans="1:11" ht="240" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>1238</v>
       </c>
@@ -18104,11 +18762,14 @@
       <c r="I312" s="2" t="s">
         <v>1239</v>
       </c>
-      <c r="J312" s="2" t="s">
+      <c r="J312" s="3" t="s">
         <v>1240</v>
       </c>
-    </row>
-    <row r="313" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K312" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="313" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>1241</v>
       </c>
@@ -18134,8 +18795,11 @@
       <c r="J313" s="2" t="s">
         <v>1243</v>
       </c>
-    </row>
-    <row r="314" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="K313" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="314" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>1244</v>
       </c>
@@ -18164,8 +18828,11 @@
       <c r="J314" s="2" t="s">
         <v>1247</v>
       </c>
-    </row>
-    <row r="315" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="K314" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="315" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>1248</v>
       </c>
@@ -18194,8 +18861,11 @@
       <c r="J315" s="2" t="s">
         <v>1251</v>
       </c>
-    </row>
-    <row r="316" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K315" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="316" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>1252</v>
       </c>
@@ -18223,8 +18893,11 @@
       <c r="J316" s="2" t="s">
         <v>1256</v>
       </c>
-    </row>
-    <row r="317" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K316" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="317" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>1257</v>
       </c>
@@ -18250,8 +18923,11 @@
       <c r="J317" s="2" t="s">
         <v>1259</v>
       </c>
-    </row>
-    <row r="318" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K317" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="318" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>1260</v>
       </c>
@@ -18277,8 +18953,11 @@
       <c r="J318" s="2" t="s">
         <v>1262</v>
       </c>
-    </row>
-    <row r="319" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+      <c r="K318" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="319" spans="1:11" ht="180" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>1263</v>
       </c>
@@ -18309,8 +18988,11 @@
       <c r="J319" s="2" t="s">
         <v>1267</v>
       </c>
-    </row>
-    <row r="320" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="K319" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="320" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>1268</v>
       </c>
@@ -18339,8 +19021,11 @@
       <c r="J320" s="2" t="s">
         <v>1272</v>
       </c>
-    </row>
-    <row r="321" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K320" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="321" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>1273</v>
       </c>
@@ -18366,8 +19051,11 @@
       <c r="J321" s="2" t="s">
         <v>1276</v>
       </c>
-    </row>
-    <row r="322" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K321" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="322" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>1277</v>
       </c>
@@ -18396,8 +19084,11 @@
       <c r="J322" s="2" t="s">
         <v>1281</v>
       </c>
-    </row>
-    <row r="323" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+      <c r="K322" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="323" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>1282</v>
       </c>
@@ -18426,8 +19117,11 @@
       <c r="J323" s="2" t="s">
         <v>1285</v>
       </c>
-    </row>
-    <row r="324" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K323" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="324" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>1286</v>
       </c>
@@ -18455,8 +19149,11 @@
       <c r="J324" s="2" t="s">
         <v>1289</v>
       </c>
-    </row>
-    <row r="325" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K324" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="325" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>1290</v>
       </c>
@@ -18482,8 +19179,11 @@
       <c r="J325" s="2" t="s">
         <v>1292</v>
       </c>
-    </row>
-    <row r="326" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K325" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="326" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>1293</v>
       </c>
@@ -18512,8 +19212,11 @@
       <c r="J326" s="2" t="s">
         <v>1297</v>
       </c>
-    </row>
-    <row r="327" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K326" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="327" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>1298</v>
       </c>
@@ -18541,8 +19244,11 @@
       <c r="J327" s="2" t="s">
         <v>1301</v>
       </c>
-    </row>
-    <row r="328" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K327" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="328" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>1302</v>
       </c>
@@ -18573,8 +19279,11 @@
       <c r="J328" s="2" t="s">
         <v>1305</v>
       </c>
-    </row>
-    <row r="329" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K328" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="329" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>1306</v>
       </c>
@@ -18603,8 +19312,11 @@
       <c r="J329" s="2" t="s">
         <v>1310</v>
       </c>
-    </row>
-    <row r="330" spans="1:10" ht="345" x14ac:dyDescent="0.25">
+      <c r="K329" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="330" spans="1:11" ht="345" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>1311</v>
       </c>
@@ -18635,8 +19347,11 @@
       <c r="J330" s="2" t="s">
         <v>1313</v>
       </c>
-    </row>
-    <row r="331" spans="1:10" ht="405" x14ac:dyDescent="0.25">
+      <c r="K330" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="331" spans="1:11" ht="405" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>1314</v>
       </c>
@@ -18665,8 +19380,11 @@
       <c r="J331" s="2" t="s">
         <v>1317</v>
       </c>
-    </row>
-    <row r="332" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K331" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="332" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>1318</v>
       </c>
@@ -18694,8 +19412,11 @@
       <c r="J332" s="2" t="s">
         <v>1321</v>
       </c>
-    </row>
-    <row r="333" spans="1:10" ht="315" x14ac:dyDescent="0.25">
+      <c r="K332" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="333" spans="1:11" ht="315" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>1322</v>
       </c>
@@ -18724,8 +19445,11 @@
       <c r="J333" s="2" t="s">
         <v>1326</v>
       </c>
-    </row>
-    <row r="334" spans="1:10" ht="240" x14ac:dyDescent="0.25">
+      <c r="K333" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="334" spans="1:11" ht="240" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>1327</v>
       </c>
@@ -18756,8 +19480,11 @@
       <c r="J334" s="2" t="s">
         <v>1330</v>
       </c>
-    </row>
-    <row r="335" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K334" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="335" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>1331</v>
       </c>
@@ -18785,8 +19512,11 @@
       <c r="J335" s="2" t="s">
         <v>1334</v>
       </c>
-    </row>
-    <row r="336" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="K335" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="336" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>1335</v>
       </c>
@@ -18814,8 +19544,11 @@
       <c r="J336" s="2" t="s">
         <v>1339</v>
       </c>
-    </row>
-    <row r="337" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="K336" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="337" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>1340</v>
       </c>
@@ -18843,8 +19576,11 @@
       <c r="J337" s="2" t="s">
         <v>1344</v>
       </c>
-    </row>
-    <row r="338" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="K337" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="338" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>1345</v>
       </c>
@@ -18872,8 +19608,11 @@
       <c r="J338" s="2" t="s">
         <v>1349</v>
       </c>
-    </row>
-    <row r="339" spans="1:10" ht="255" x14ac:dyDescent="0.25">
+      <c r="K338" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="339" spans="1:11" ht="255" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>1350</v>
       </c>
@@ -18904,8 +19643,11 @@
       <c r="J339" s="2" t="s">
         <v>1354</v>
       </c>
-    </row>
-    <row r="340" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K339" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="340" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>1355</v>
       </c>
@@ -18933,8 +19675,11 @@
       <c r="J340" s="2" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="341" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K340" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="341" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>1360</v>
       </c>
@@ -18962,8 +19707,11 @@
       <c r="J341" s="2" t="s">
         <v>1363</v>
       </c>
-    </row>
-    <row r="342" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K341" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="342" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>1364</v>
       </c>
@@ -18992,8 +19740,11 @@
       <c r="J342" s="2" t="s">
         <v>1367</v>
       </c>
-    </row>
-    <row r="343" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K342" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="343" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>1368</v>
       </c>
@@ -19019,8 +19770,11 @@
       <c r="J343" s="2" t="s">
         <v>1370</v>
       </c>
-    </row>
-    <row r="344" spans="1:10" ht="405" x14ac:dyDescent="0.25">
+      <c r="K343" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="344" spans="1:11" ht="405" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>1371</v>
       </c>
@@ -19049,8 +19803,11 @@
       <c r="J344" s="2" t="s">
         <v>1374</v>
       </c>
-    </row>
-    <row r="345" spans="1:10" ht="375" x14ac:dyDescent="0.25">
+      <c r="K344" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="345" spans="1:11" ht="375" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>1375</v>
       </c>
@@ -19079,8 +19836,11 @@
       <c r="J345" s="2" t="s">
         <v>1378</v>
       </c>
-    </row>
-    <row r="346" spans="1:10" ht="345" x14ac:dyDescent="0.25">
+      <c r="K345" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="346" spans="1:11" ht="345" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>1379</v>
       </c>
@@ -19111,8 +19871,11 @@
       <c r="J346" s="2" t="s">
         <v>1384</v>
       </c>
-    </row>
-    <row r="347" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K346" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="347" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>1385</v>
       </c>
@@ -19141,8 +19904,11 @@
       <c r="J347" s="2" t="s">
         <v>1388</v>
       </c>
-    </row>
-    <row r="348" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K347" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="348" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>1389</v>
       </c>
@@ -19173,8 +19939,11 @@
       <c r="J348" s="2" t="s">
         <v>1392</v>
       </c>
-    </row>
-    <row r="349" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K348" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="349" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>1393</v>
       </c>
@@ -19205,8 +19974,11 @@
       <c r="J349" s="2" t="s">
         <v>1397</v>
       </c>
-    </row>
-    <row r="350" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K349" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="350" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>1398</v>
       </c>
@@ -19237,8 +20009,11 @@
       <c r="J350" s="2" t="s">
         <v>1403</v>
       </c>
-    </row>
-    <row r="351" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K350" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="351" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>1404</v>
       </c>
@@ -19266,8 +20041,11 @@
       <c r="J351" s="2" t="s">
         <v>1406</v>
       </c>
-    </row>
-    <row r="352" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K351" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="352" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>1407</v>
       </c>
@@ -19295,8 +20073,11 @@
       <c r="J352" s="2" t="s">
         <v>1412</v>
       </c>
-    </row>
-    <row r="353" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K352" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="353" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>1413</v>
       </c>
@@ -19324,8 +20105,11 @@
       <c r="J353" s="2" t="s">
         <v>1417</v>
       </c>
-    </row>
-    <row r="354" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K353" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="354" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>1418</v>
       </c>
@@ -19356,8 +20140,11 @@
       <c r="J354" s="2" t="s">
         <v>1422</v>
       </c>
-    </row>
-    <row r="355" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K354" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="355" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>1423</v>
       </c>
@@ -19385,8 +20172,11 @@
       <c r="J355" s="2" t="s">
         <v>1427</v>
       </c>
-    </row>
-    <row r="356" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K355" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="356" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>1428</v>
       </c>
@@ -19414,8 +20204,11 @@
       <c r="J356" s="2" t="s">
         <v>1431</v>
       </c>
-    </row>
-    <row r="357" spans="1:10" ht="240" x14ac:dyDescent="0.25">
+      <c r="K356" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="357" spans="1:11" ht="240" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>1432</v>
       </c>
@@ -19443,8 +20236,11 @@
       <c r="J357" s="2" t="s">
         <v>1434</v>
       </c>
-    </row>
-    <row r="358" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="K357" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="358" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>1435</v>
       </c>
@@ -19473,8 +20269,11 @@
       <c r="J358" s="2" t="s">
         <v>1438</v>
       </c>
-    </row>
-    <row r="359" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K358" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="359" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>1439</v>
       </c>
@@ -19502,8 +20301,11 @@
       <c r="J359" s="2" t="s">
         <v>1442</v>
       </c>
-    </row>
-    <row r="360" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K359" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="360" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>1443</v>
       </c>
@@ -19531,8 +20333,11 @@
       <c r="J360" s="2" t="s">
         <v>1446</v>
       </c>
-    </row>
-    <row r="361" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K360" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="361" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>1447</v>
       </c>
@@ -19560,8 +20365,11 @@
       <c r="J361" s="2" t="s">
         <v>1450</v>
       </c>
-    </row>
-    <row r="362" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+      <c r="K361" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="362" spans="1:11" ht="210" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>1451</v>
       </c>
@@ -19591,7 +20399,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="363" spans="1:10" ht="345" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:11" ht="345" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>1455</v>
       </c>
@@ -19620,7 +20428,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="364" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>1459</v>
       </c>
@@ -19649,7 +20457,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="365" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>1463</v>
       </c>
@@ -19678,8 +20486,11 @@
       <c r="J365" s="2" t="s">
         <v>1467</v>
       </c>
-    </row>
-    <row r="366" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="K365" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="366" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>1468</v>
       </c>
@@ -19707,8 +20518,11 @@
       <c r="J366" s="2" t="s">
         <v>1471</v>
       </c>
-    </row>
-    <row r="367" spans="1:10" ht="375" x14ac:dyDescent="0.25">
+      <c r="K366" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="367" spans="1:11" ht="375" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>1472</v>
       </c>
@@ -19736,8 +20550,11 @@
       <c r="J367" s="2" t="s">
         <v>1473</v>
       </c>
-    </row>
-    <row r="368" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K367" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="368" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>1474</v>
       </c>
@@ -19763,8 +20580,11 @@
       <c r="J368" s="2" t="s">
         <v>1477</v>
       </c>
-    </row>
-    <row r="369" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K368" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="369" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>1478</v>
       </c>
@@ -19790,8 +20610,11 @@
       <c r="J369" s="2" t="s">
         <v>1480</v>
       </c>
-    </row>
-    <row r="370" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K369" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="370" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>1481</v>
       </c>
@@ -19817,8 +20640,11 @@
       <c r="J370" s="2" t="s">
         <v>1483</v>
       </c>
-    </row>
-    <row r="371" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="K370" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="371" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>1484</v>
       </c>
@@ -19844,8 +20670,11 @@
       <c r="J371" s="2" t="s">
         <v>1486</v>
       </c>
-    </row>
-    <row r="372" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K371" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="372" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>1487</v>
       </c>
@@ -19873,8 +20702,11 @@
       <c r="J372" s="2" t="s">
         <v>1491</v>
       </c>
-    </row>
-    <row r="373" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="K372" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="373" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>1492</v>
       </c>
@@ -19900,8 +20732,11 @@
       <c r="J373" s="2" t="s">
         <v>1494</v>
       </c>
-    </row>
-    <row r="374" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K373" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="374" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>1495</v>
       </c>
@@ -19929,8 +20764,11 @@
       <c r="J374" s="2" t="s">
         <v>1499</v>
       </c>
-    </row>
-    <row r="375" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K374" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="375" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>1500</v>
       </c>
@@ -19956,8 +20794,11 @@
       <c r="J375" s="2" t="s">
         <v>1503</v>
       </c>
-    </row>
-    <row r="376" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="K375" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="376" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>1504</v>
       </c>
@@ -19985,8 +20826,11 @@
       <c r="J376" s="2" t="s">
         <v>1507</v>
       </c>
-    </row>
-    <row r="377" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K376" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="377" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>1508</v>
       </c>
@@ -20014,8 +20858,11 @@
       <c r="J377" s="2" t="s">
         <v>1512</v>
       </c>
-    </row>
-    <row r="378" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K377" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="378" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>1513</v>
       </c>
@@ -20041,8 +20888,11 @@
       <c r="J378" s="2" t="s">
         <v>1514</v>
       </c>
-    </row>
-    <row r="379" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="K378" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="379" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>1515</v>
       </c>
@@ -20068,8 +20918,11 @@
       <c r="J379" s="2" t="s">
         <v>1518</v>
       </c>
-    </row>
-    <row r="380" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K379" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="380" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>1519</v>
       </c>
@@ -20095,8 +20948,11 @@
       <c r="J380" s="2" t="s">
         <v>1522</v>
       </c>
-    </row>
-    <row r="381" spans="1:10" ht="225" x14ac:dyDescent="0.25">
+      <c r="K380" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="381" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>1523</v>
       </c>
@@ -20124,8 +20980,11 @@
       <c r="J381" s="2" t="s">
         <v>1527</v>
       </c>
-    </row>
-    <row r="382" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K381" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="382" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>1528</v>
       </c>
@@ -20153,8 +21012,11 @@
       <c r="J382" s="2" t="s">
         <v>1531</v>
       </c>
-    </row>
-    <row r="383" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K382" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="383" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>1532</v>
       </c>
@@ -20182,8 +21044,11 @@
       <c r="J383" s="2" t="s">
         <v>1535</v>
       </c>
-    </row>
-    <row r="384" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="K383" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="384" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>1536</v>
       </c>
@@ -20209,8 +21074,11 @@
       <c r="J384" s="2" t="s">
         <v>1538</v>
       </c>
-    </row>
-    <row r="385" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K384" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="385" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>1539</v>
       </c>
@@ -20241,8 +21109,11 @@
       <c r="J385" s="2" t="s">
         <v>1543</v>
       </c>
-    </row>
-    <row r="386" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K385" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="386" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>1544</v>
       </c>
@@ -20268,8 +21139,11 @@
       <c r="J386" s="2" t="s">
         <v>1547</v>
       </c>
-    </row>
-    <row r="387" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K386" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="387" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>1548</v>
       </c>
@@ -20295,8 +21169,11 @@
       <c r="J387" s="2" t="s">
         <v>1550</v>
       </c>
-    </row>
-    <row r="388" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K387" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="388" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>1551</v>
       </c>
@@ -20325,8 +21202,11 @@
       <c r="J388" s="2" t="s">
         <v>1555</v>
       </c>
-    </row>
-    <row r="389" spans="1:10" ht="255" x14ac:dyDescent="0.25">
+      <c r="K388" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="389" spans="1:11" ht="255" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>1556</v>
       </c>
@@ -20352,8 +21232,11 @@
       <c r="J389" s="2" t="s">
         <v>1557</v>
       </c>
-    </row>
-    <row r="390" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K389" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="390" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>1558</v>
       </c>
@@ -20379,8 +21262,11 @@
       <c r="J390" s="2" t="s">
         <v>1561</v>
       </c>
-    </row>
-    <row r="391" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K390" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="391" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>1562</v>
       </c>
@@ -20406,8 +21292,11 @@
       <c r="J391" s="2" t="s">
         <v>1565</v>
       </c>
-    </row>
-    <row r="392" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K391" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="392" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>1566</v>
       </c>
@@ -20433,8 +21322,11 @@
       <c r="J392" s="2" t="s">
         <v>1568</v>
       </c>
-    </row>
-    <row r="393" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="K392" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="393" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>1569</v>
       </c>
@@ -20460,8 +21352,11 @@
       <c r="J393" s="2" t="s">
         <v>1572</v>
       </c>
-    </row>
-    <row r="394" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K393" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="394" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>1573</v>
       </c>
@@ -20487,8 +21382,11 @@
       <c r="J394" s="2" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="395" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K394" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="395" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>1577</v>
       </c>
@@ -20514,8 +21412,11 @@
       <c r="J395" s="2" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="396" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K395" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="396" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>1580</v>
       </c>
@@ -20541,8 +21442,11 @@
       <c r="J396" s="2" t="s">
         <v>1583</v>
       </c>
-    </row>
-    <row r="397" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K396" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="397" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>1584</v>
       </c>
@@ -20571,8 +21475,11 @@
       <c r="J397" s="2" t="s">
         <v>1587</v>
       </c>
-    </row>
-    <row r="398" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K397" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="398" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>1588</v>
       </c>
@@ -20600,8 +21507,11 @@
       <c r="J398" s="2" t="s">
         <v>1592</v>
       </c>
-    </row>
-    <row r="399" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K398" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="399" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>1593</v>
       </c>
@@ -20630,8 +21540,11 @@
       <c r="J399" s="2" t="s">
         <v>1595</v>
       </c>
-    </row>
-    <row r="400" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K399" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="400" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>1596</v>
       </c>
@@ -20659,8 +21572,11 @@
       <c r="J400" s="2" t="s">
         <v>1600</v>
       </c>
-    </row>
-    <row r="401" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K400" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="401" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>1601</v>
       </c>
@@ -20688,8 +21604,11 @@
       <c r="J401" s="2" t="s">
         <v>1604</v>
       </c>
-    </row>
-    <row r="402" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K401" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="402" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>1605</v>
       </c>
@@ -20718,8 +21637,11 @@
       <c r="J402" s="2" t="s">
         <v>1609</v>
       </c>
-    </row>
-    <row r="403" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+      <c r="K402" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="403" spans="1:11" ht="165" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>1610</v>
       </c>
@@ -20748,8 +21670,11 @@
       <c r="J403" s="2" t="s">
         <v>1614</v>
       </c>
-    </row>
-    <row r="404" spans="1:10" ht="390" x14ac:dyDescent="0.25">
+      <c r="K403" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="404" spans="1:11" ht="390" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>1615</v>
       </c>
@@ -20775,8 +21700,11 @@
       <c r="J404" s="2" t="s">
         <v>1618</v>
       </c>
-    </row>
-    <row r="405" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K404" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="405" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>1619</v>
       </c>
@@ -20805,7 +21733,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="406" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:11" ht="180" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>1623</v>
       </c>
@@ -20832,7 +21760,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="407" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>1626</v>
       </c>
@@ -20858,8 +21786,11 @@
       <c r="J407" s="2" t="s">
         <v>1629</v>
       </c>
-    </row>
-    <row r="408" spans="1:10" ht="195" x14ac:dyDescent="0.25">
+      <c r="K407" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="408" spans="1:11" ht="195" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>1630</v>
       </c>
@@ -20885,8 +21816,11 @@
       <c r="J408" s="2" t="s">
         <v>1633</v>
       </c>
-    </row>
-    <row r="409" spans="1:10" ht="270" x14ac:dyDescent="0.25">
+      <c r="K408" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="409" spans="1:11" ht="270" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>1634</v>
       </c>
@@ -20914,8 +21848,11 @@
       <c r="J409" s="2" t="s">
         <v>1637</v>
       </c>
-    </row>
-    <row r="410" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K409" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="410" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>1638</v>
       </c>
@@ -20943,8 +21880,11 @@
       <c r="J410" s="2" t="s">
         <v>1642</v>
       </c>
-    </row>
-    <row r="411" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K410" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="411" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>1643</v>
       </c>
@@ -20973,8 +21913,11 @@
       <c r="J411" s="2" t="s">
         <v>1646</v>
       </c>
-    </row>
-    <row r="412" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="K411" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="412" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>1647</v>
       </c>
@@ -21000,8 +21943,11 @@
       <c r="J412" s="2" t="s">
         <v>1650</v>
       </c>
-    </row>
-    <row r="413" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K412" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="413" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>1651</v>
       </c>
@@ -21029,8 +21975,11 @@
       <c r="J413" s="2" t="s">
         <v>1655</v>
       </c>
-    </row>
-    <row r="414" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K413" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="414" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>1656</v>
       </c>
@@ -21058,8 +22007,11 @@
       <c r="J414" s="2" t="s">
         <v>1659</v>
       </c>
-    </row>
-    <row r="415" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K414" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="415" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>1660</v>
       </c>
@@ -21087,8 +22039,11 @@
       <c r="J415" s="2" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="416" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+      <c r="K415" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="416" spans="1:11" ht="210" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>1664</v>
       </c>
@@ -21119,8 +22074,11 @@
       <c r="J416" s="2" t="s">
         <v>1667</v>
       </c>
-    </row>
-    <row r="417" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+      <c r="K416" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="417" spans="1:11" ht="180" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>1668</v>
       </c>
@@ -21150,7 +22108,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="418" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>1672</v>
       </c>
@@ -21179,7 +22137,7 @@
         <v>1674</v>
       </c>
     </row>
-    <row r="419" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:11" ht="180" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>1675</v>
       </c>
@@ -21207,8 +22165,11 @@
       <c r="J419" s="2" t="s">
         <v>1678</v>
       </c>
-    </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K419" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>1679</v>
       </c>
@@ -21238,7 +22199,7 @@
         <v>1682</v>
       </c>
     </row>
-    <row r="421" spans="1:10" ht="405" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:11" ht="405" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>1683</v>
       </c>
@@ -21264,8 +22225,11 @@
       <c r="J421" s="2" t="s">
         <v>1685</v>
       </c>
-    </row>
-    <row r="422" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K421" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="422" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>1686</v>
       </c>
@@ -21291,8 +22255,11 @@
       <c r="J422" s="2" t="s">
         <v>1689</v>
       </c>
-    </row>
-    <row r="423" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K422" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="423" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>1690</v>
       </c>
@@ -21321,8 +22288,11 @@
       <c r="J423" s="2" t="s">
         <v>1694</v>
       </c>
-    </row>
-    <row r="424" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+      <c r="K423" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="424" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>1695</v>
       </c>
@@ -21353,8 +22323,11 @@
       <c r="J424" s="2" t="s">
         <v>1698</v>
       </c>
-    </row>
-    <row r="425" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K424" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="425" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>1699</v>
       </c>
@@ -21380,8 +22353,11 @@
       <c r="J425" s="2" t="s">
         <v>1702</v>
       </c>
-    </row>
-    <row r="426" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K425" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="426" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>1703</v>
       </c>
@@ -21410,8 +22386,11 @@
       <c r="J426" s="2" t="s">
         <v>1707</v>
       </c>
-    </row>
-    <row r="427" spans="1:10" ht="195" x14ac:dyDescent="0.25">
+      <c r="K426" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="427" spans="1:11" ht="195" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>1708</v>
       </c>
@@ -21442,8 +22421,11 @@
       <c r="J427" s="2" t="s">
         <v>1712</v>
       </c>
-    </row>
-    <row r="428" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K427" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="428" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>1713</v>
       </c>
@@ -21471,8 +22453,11 @@
       <c r="J428" s="2" t="s">
         <v>1717</v>
       </c>
-    </row>
-    <row r="429" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K428" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="429" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>1718</v>
       </c>
@@ -21501,8 +22486,11 @@
       <c r="J429" s="2" t="s">
         <v>1721</v>
       </c>
-    </row>
-    <row r="430" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K429" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="430" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>1722</v>
       </c>
@@ -21531,8 +22519,11 @@
       <c r="J430" s="2" t="s">
         <v>1726</v>
       </c>
-    </row>
-    <row r="431" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K430" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="431" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>1727</v>
       </c>
@@ -21561,8 +22552,11 @@
       <c r="J431" s="2" t="s">
         <v>1729</v>
       </c>
-    </row>
-    <row r="432" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K431" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="432" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>1730</v>
       </c>
@@ -21593,8 +22587,11 @@
       <c r="J432" s="2" t="s">
         <v>1735</v>
       </c>
-    </row>
-    <row r="433" spans="1:10" ht="315" x14ac:dyDescent="0.25">
+      <c r="K432" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="433" spans="1:11" ht="315" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>1736</v>
       </c>
@@ -21623,8 +22620,11 @@
       <c r="J433" s="2" t="s">
         <v>1738</v>
       </c>
-    </row>
-    <row r="434" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K433" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="434" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>1739</v>
       </c>
@@ -21653,8 +22653,11 @@
       <c r="J434" s="2" t="s">
         <v>1742</v>
       </c>
-    </row>
-    <row r="435" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K434" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="435" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>1743</v>
       </c>
@@ -21682,8 +22685,11 @@
       <c r="J435" s="2" t="s">
         <v>1747</v>
       </c>
-    </row>
-    <row r="436" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+      <c r="K435" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="436" spans="1:11" ht="165" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>1748</v>
       </c>
@@ -21712,8 +22718,11 @@
       <c r="J436" s="2" t="s">
         <v>1752</v>
       </c>
-    </row>
-    <row r="437" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+      <c r="K436" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="437" spans="1:11" ht="165" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>1753</v>
       </c>
@@ -21742,8 +22751,11 @@
       <c r="J437" s="2" t="s">
         <v>1755</v>
       </c>
-    </row>
-    <row r="438" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K437" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="438" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>1756</v>
       </c>
@@ -21772,8 +22784,11 @@
       <c r="J438" s="2" t="s">
         <v>1759</v>
       </c>
-    </row>
-    <row r="439" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="K438" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="439" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>1760</v>
       </c>
@@ -21799,8 +22814,11 @@
       <c r="J439" s="2" t="s">
         <v>1763</v>
       </c>
-    </row>
-    <row r="440" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K439" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="440" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>1764</v>
       </c>
@@ -21828,8 +22846,11 @@
       <c r="J440" s="2" t="s">
         <v>1767</v>
       </c>
-    </row>
-    <row r="441" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K440" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="441" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>1768</v>
       </c>
@@ -21857,8 +22878,11 @@
       <c r="J441" s="2" t="s">
         <v>1771</v>
       </c>
-    </row>
-    <row r="442" spans="1:10" ht="375" x14ac:dyDescent="0.25">
+      <c r="K441" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="442" spans="1:11" ht="375" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>1772</v>
       </c>
@@ -21887,8 +22911,11 @@
       <c r="J442" s="2" t="s">
         <v>1775</v>
       </c>
-    </row>
-    <row r="443" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K442" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="443" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>1776</v>
       </c>
@@ -21914,8 +22941,11 @@
       <c r="J443" s="2" t="s">
         <v>1779</v>
       </c>
-    </row>
-    <row r="444" spans="1:10" ht="345" x14ac:dyDescent="0.25">
+      <c r="K443" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="444" spans="1:11" ht="345" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>1780</v>
       </c>
@@ -21946,8 +22976,11 @@
       <c r="J444" s="2" t="s">
         <v>1782</v>
       </c>
-    </row>
-    <row r="445" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="K444" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="445" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>1783</v>
       </c>
@@ -21976,8 +23009,11 @@
       <c r="J445" s="2" t="s">
         <v>1787</v>
       </c>
-    </row>
-    <row r="446" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+      <c r="K445" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="446" spans="1:11" ht="165" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>1788</v>
       </c>
@@ -22005,8 +23041,11 @@
       <c r="J446" s="2" t="s">
         <v>1792</v>
       </c>
-    </row>
-    <row r="447" spans="1:10" ht="255" x14ac:dyDescent="0.25">
+      <c r="K446" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="447" spans="1:11" ht="255" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>1793</v>
       </c>
@@ -22037,8 +23076,11 @@
       <c r="J447" s="2" t="s">
         <v>1797</v>
       </c>
-    </row>
-    <row r="448" spans="1:10" ht="240" x14ac:dyDescent="0.25">
+      <c r="K447" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="448" spans="1:11" ht="240" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>1798</v>
       </c>
@@ -22067,8 +23109,11 @@
       <c r="J448" s="2" t="s">
         <v>1801</v>
       </c>
-    </row>
-    <row r="449" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+      <c r="K448" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="449" spans="1:11" ht="135" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>1802</v>
       </c>
@@ -22097,8 +23142,11 @@
       <c r="J449" s="2" t="s">
         <v>1804</v>
       </c>
-    </row>
-    <row r="450" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K449" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="450" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>1805</v>
       </c>
@@ -22127,8 +23175,11 @@
       <c r="J450" s="2" t="s">
         <v>1808</v>
       </c>
-    </row>
-    <row r="451" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+      <c r="K450" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="451" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>1809</v>
       </c>
@@ -22157,8 +23208,11 @@
       <c r="J451" s="2" t="s">
         <v>1812</v>
       </c>
-    </row>
-    <row r="452" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K451" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="452" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>1813</v>
       </c>
@@ -22189,8 +23243,11 @@
       <c r="J452" s="2" t="s">
         <v>1818</v>
       </c>
-    </row>
-    <row r="453" spans="1:10" ht="375" x14ac:dyDescent="0.25">
+      <c r="K452" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="453" spans="1:11" ht="375" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>1819</v>
       </c>
@@ -22218,8 +23275,11 @@
       <c r="J453" s="2" t="s">
         <v>1822</v>
       </c>
-    </row>
-    <row r="454" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+      <c r="K453" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="454" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>1823</v>
       </c>
@@ -22248,8 +23308,11 @@
       <c r="J454" s="2" t="s">
         <v>1827</v>
       </c>
-    </row>
-    <row r="455" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K454" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="455" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>1828</v>
       </c>
@@ -22277,8 +23340,11 @@
       <c r="J455" s="2" t="s">
         <v>1831</v>
       </c>
-    </row>
-    <row r="456" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K455" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="456" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>1832</v>
       </c>
@@ -22309,8 +23375,11 @@
       <c r="J456" s="2" t="s">
         <v>1837</v>
       </c>
-    </row>
-    <row r="457" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K456" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="457" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>1838</v>
       </c>
@@ -22336,8 +23405,11 @@
       <c r="J457" s="2" t="s">
         <v>1840</v>
       </c>
-    </row>
-    <row r="458" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K457" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="458" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>1841</v>
       </c>
@@ -22363,8 +23435,11 @@
       <c r="J458" s="2" t="s">
         <v>1843</v>
       </c>
-    </row>
-    <row r="459" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K458" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="459" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>1844</v>
       </c>
@@ -22395,8 +23470,11 @@
       <c r="J459" s="2" t="s">
         <v>1847</v>
       </c>
-    </row>
-    <row r="460" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K459" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="460" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>1848</v>
       </c>
@@ -22422,8 +23500,11 @@
       <c r="J460" s="2" t="s">
         <v>1850</v>
       </c>
-    </row>
-    <row r="461" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K460" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="461" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>1851</v>
       </c>
@@ -22449,8 +23530,11 @@
       <c r="J461" s="2" t="s">
         <v>1853</v>
       </c>
-    </row>
-    <row r="462" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K461" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="462" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>1854</v>
       </c>
@@ -22479,8 +23563,11 @@
       <c r="J462" s="2" t="s">
         <v>1857</v>
       </c>
-    </row>
-    <row r="463" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K462" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="463" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>1858</v>
       </c>
@@ -22509,8 +23596,11 @@
       <c r="J463" s="2" t="s">
         <v>1862</v>
       </c>
-    </row>
-    <row r="464" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K463" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="464" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>1863</v>
       </c>
@@ -22539,8 +23629,11 @@
       <c r="J464" s="2" t="s">
         <v>1867</v>
       </c>
-    </row>
-    <row r="465" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K464" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="465" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>1868</v>
       </c>
@@ -22569,8 +23662,11 @@
       <c r="J465" s="2" t="s">
         <v>1871</v>
       </c>
-    </row>
-    <row r="466" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K465" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="466" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>1872</v>
       </c>
@@ -22599,8 +23695,11 @@
       <c r="J466" s="2" t="s">
         <v>1875</v>
       </c>
-    </row>
-    <row r="467" spans="1:10" ht="285" x14ac:dyDescent="0.25">
+      <c r="K466" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="467" spans="1:11" ht="285" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>1876</v>
       </c>
@@ -22629,8 +23728,11 @@
       <c r="J467" s="2" t="s">
         <v>1880</v>
       </c>
-    </row>
-    <row r="468" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+      <c r="K467" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="468" spans="1:11" ht="135" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>1881</v>
       </c>
@@ -22659,8 +23761,11 @@
       <c r="J468" s="2" t="s">
         <v>1885</v>
       </c>
-    </row>
-    <row r="469" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+      <c r="K468" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="469" spans="1:11" ht="210" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>1886</v>
       </c>
@@ -22689,8 +23794,11 @@
       <c r="J469" s="2" t="s">
         <v>1890</v>
       </c>
-    </row>
-    <row r="470" spans="1:10" ht="225" x14ac:dyDescent="0.25">
+      <c r="K469" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="470" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>1891</v>
       </c>
@@ -22719,8 +23827,11 @@
       <c r="J470" s="2" t="s">
         <v>1894</v>
       </c>
-    </row>
-    <row r="471" spans="1:10" ht="360" x14ac:dyDescent="0.25">
+      <c r="K470" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="471" spans="1:11" ht="360" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>1895</v>
       </c>
@@ -22749,8 +23860,11 @@
       <c r="J471" s="2" t="s">
         <v>1898</v>
       </c>
-    </row>
-    <row r="472" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+      <c r="K471" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="472" spans="1:11" ht="165" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>1899</v>
       </c>
@@ -22778,8 +23892,11 @@
       <c r="J472" s="2" t="s">
         <v>1903</v>
       </c>
-    </row>
-    <row r="473" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K472" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="473" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>1904</v>
       </c>
@@ -22808,8 +23925,11 @@
       <c r="J473" s="2" t="s">
         <v>1908</v>
       </c>
-    </row>
-    <row r="474" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K473" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="474" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>1909</v>
       </c>
@@ -22835,8 +23955,11 @@
       <c r="J474" s="2" t="s">
         <v>1912</v>
       </c>
-    </row>
-    <row r="475" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="K474" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="475" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>1913</v>
       </c>
@@ -22865,8 +23988,11 @@
       <c r="J475" s="2" t="s">
         <v>1916</v>
       </c>
-    </row>
-    <row r="476" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="K475" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="476" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>1917</v>
       </c>
@@ -22897,8 +24023,11 @@
       <c r="J476" s="2" t="s">
         <v>1922</v>
       </c>
-    </row>
-    <row r="477" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K476" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="477" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>1923</v>
       </c>
@@ -22927,8 +24056,11 @@
       <c r="J477" s="2" t="s">
         <v>1926</v>
       </c>
-    </row>
-    <row r="478" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K477" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="478" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>1927</v>
       </c>
@@ -22957,8 +24089,11 @@
       <c r="J478" s="2" t="s">
         <v>1931</v>
       </c>
-    </row>
-    <row r="479" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K478" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="479" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>1932</v>
       </c>
@@ -22987,8 +24122,11 @@
       <c r="J479" s="2" t="s">
         <v>1934</v>
       </c>
-    </row>
-    <row r="480" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K479" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="480" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>1935</v>
       </c>
@@ -23014,8 +24152,11 @@
       <c r="J480" s="2" t="s">
         <v>1938</v>
       </c>
-    </row>
-    <row r="481" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="K480" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="481" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>1939</v>
       </c>
@@ -23044,8 +24185,11 @@
       <c r="J481" s="2" t="s">
         <v>1943</v>
       </c>
-    </row>
-    <row r="482" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K481" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="482" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>1944</v>
       </c>
@@ -23074,8 +24218,11 @@
       <c r="J482" s="2" t="s">
         <v>1947</v>
       </c>
-    </row>
-    <row r="483" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K482" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="483" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>1948</v>
       </c>
@@ -23103,8 +24250,11 @@
       <c r="J483" s="2" t="s">
         <v>1952</v>
       </c>
-    </row>
-    <row r="484" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="K483" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="484" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>1953</v>
       </c>
@@ -23133,8 +24283,11 @@
       <c r="J484" s="2" t="s">
         <v>1957</v>
       </c>
-    </row>
-    <row r="485" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="K484" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="485" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>1958</v>
       </c>
@@ -23163,8 +24316,11 @@
       <c r="J485" s="2" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="486" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K485" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="486" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>1962</v>
       </c>
@@ -23193,8 +24349,11 @@
       <c r="J486" s="2" t="s">
         <v>1966</v>
       </c>
-    </row>
-    <row r="487" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K486" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="487" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>1967</v>
       </c>
@@ -23223,8 +24382,11 @@
       <c r="J487" s="2" t="s">
         <v>1971</v>
       </c>
-    </row>
-    <row r="488" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="K487" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="488" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>1972</v>
       </c>
@@ -23252,6 +24414,9 @@
       </c>
       <c r="J488" s="2" t="s">
         <v>1976</v>
+      </c>
+      <c r="K488" s="2" t="s">
+        <v>1979</v>
       </c>
     </row>
   </sheetData>
